--- a/Students.xlsx
+++ b/Students.xlsx
@@ -5624,17 +5624,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>922525106036</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BALARITHISH S</t>
+          <t>Arulesh K</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/3/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>922525106035</t>
+          <t>922525106036</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BALAJI C</t>
+          <t>BALARITHISH S</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/4/</t>
+          <t>https://leetcode.com/u/3/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>922525106058</t>
+          <t>922525106035</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DEEKSHA K</t>
+          <t>BALAJI C</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/5/</t>
+          <t>https://leetcode.com/u/4/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>922525106058</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AJAYKRISHNA R</t>
+          <t>DEEKSHA K</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106011/</t>
+          <t>https://leetcode.com/u/5/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>AJAYKRISHNA R</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106049/</t>
+          <t>https://leetcode.com/u/922525106011/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CHINMAYASRI K</t>
+          <t>BUVNESH N</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106052/</t>
+          <t>https://leetcode.com/u/922525106049/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DARSHAN C</t>
+          <t>CHINMAYASRI K</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5806,51 +5806,51 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106055/</t>
+          <t>https://leetcode.com/u/922525106052/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GIRIVASH P</t>
+          <t>DARSHAN C</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106093/</t>
+          <t>https://leetcode.com/u/922525106055/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GOPALA KRISHNAN C</t>
+          <t>GIRIVASH P</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5860,24 +5860,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106096/</t>
+          <t>https://leetcode.com/u/922525106093/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GOPINATH R</t>
+          <t>GOPALA KRISHNAN C</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5887,51 +5887,51 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106097/</t>
+          <t>https://leetcode.com/u/922525106096/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>922525106056</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DARSHAN MANISH A</t>
+          <t>GOPINATH R</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2007darshan</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/2007darshan/</t>
+          <t>https://leetcode.com/u/922525106097/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106056</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>DARSHAN MANISH A</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>2007darshan</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5941,24 +5941,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/2007darshan/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106013</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AJITH KUMAR M</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ajit_kumar_23</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>922525106019</t>
+          <t>922525106013</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ANBARASU S</t>
+          <t>AJITH KUMAR M</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Anbarasu28122007</t>
+          <t>ajit_kumar_23</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106020</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANJITHAA N</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>Anjithaa2006</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Arulesh K</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106020</t>
+          <t>922525106019</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ANJITHAA N</t>
+          <t>ANBARASU S</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Anjithaa2006</t>
+          <t>Anbarasu28122007</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
@@ -5651,17 +5651,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>922525106036</t>
+          <t>922525106040</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BALARITHISH S</t>
+          <t>BHARANIDHARAN S</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bharanidharan_2007</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/3/</t>
+          <t>https://leetcode.com/u/Bharanidharan_2007/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>922525106035</t>
+          <t>922525106036</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>BALAJI C</t>
+          <t>BALARITHISH S</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/4/</t>
+          <t>https://leetcode.com/u/3/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>922525106058</t>
+          <t>922525106035</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DEEKSHA K</t>
+          <t>BALAJI C</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/5/</t>
+          <t>https://leetcode.com/u/4/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>922525106058</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AJAYKRISHNA R</t>
+          <t>DEEKSHA K</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106011/</t>
+          <t>https://leetcode.com/u/5/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>AJAYKRISHNA R</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106049/</t>
+          <t>https://leetcode.com/u/922525106011/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CHINMAYASRI K</t>
+          <t>BUVNESH N</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106052/</t>
+          <t>https://leetcode.com/u/922525106049/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DARSHAN C</t>
+          <t>CHINMAYASRI K</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5833,51 +5833,51 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106055/</t>
+          <t>https://leetcode.com/u/922525106052/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GIRIVASH P</t>
+          <t>DARSHAN C</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106093/</t>
+          <t>https://leetcode.com/u/922525106055/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GOPALA KRISHNAN C</t>
+          <t>GIRIVASH P</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106096/</t>
+          <t>https://leetcode.com/u/922525106093/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GOPINATH R</t>
+          <t>GOPALA KRISHNAN C</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5914,51 +5914,51 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106097/</t>
+          <t>https://leetcode.com/u/922525106096/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>922525106056</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DARSHAN MANISH A</t>
+          <t>GOPINATH R</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2007darshan</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/2007darshan/</t>
+          <t>https://leetcode.com/u/922525106097/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106056</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>DARSHAN MANISH A</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>2007darshan</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/2007darshan/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>922525106013</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AJITH KUMAR M</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ajit_kumar_23</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>922525106020</t>
+          <t>922525106019</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ANJITHAA N</t>
+          <t>ANBARASU S</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Anjithaa2006</t>
+          <t>Anbarasu28122007</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106020</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANJITHAA N</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>Anjithaa2006</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>922525106008</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>AHELESH G S</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/B/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>922525106037</t>
+          <t>922525106008</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>BARANITHARAN V</t>
+          <t>AHELESH G S</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>barani_7</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/barani_7/</t>
+          <t>https://leetcode.com/u/B/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>922525106039</t>
+          <t>922525106037</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>BENOV NAVIN V</t>
+          <t>BARANITHARAN V</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Benov_18</t>
+          <t>barani_7</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Benov_18/</t>
+          <t>https://leetcode.com/u/barani_7/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>922525106044</t>
+          <t>922525106039</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Bhavan bala N</t>
+          <t>BENOV NAVIN V</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BhavanBala</t>
+          <t>Benov_18</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BhavanBala/</t>
+          <t>https://leetcode.com/u/Benov_18/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>922525106041</t>
+          <t>922525106044</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BHARATH KUMAR E</t>
+          <t>Bhavan bala N</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BK5226221</t>
+          <t>BhavanBala</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BK5226221/</t>
+          <t>https://leetcode.com/u/BhavanBala/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>922525106045</t>
+          <t>922525106041</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>BOOBASE R</t>
+          <t>BHARATH KUMAR E</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Boobase</t>
+          <t>BK5226221</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Boobase/</t>
+          <t>https://leetcode.com/u/BK5226221/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>922525106046</t>
+          <t>922525106045</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>BOOMIKA T</t>
+          <t>BOOBASE R</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>boomikat123</t>
+          <t>Boobase</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/boomikat123/</t>
+          <t>https://leetcode.com/u/Boobase/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106046</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>BOOMIKA T</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>boomikat123</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/boomikat123/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>922525106048</t>
+          <t>922525106047</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>BRINDHA S</t>
+          <t>BOSVIYA P</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Brindha_S</t>
+          <t>BosviyaBSV</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Brindha_S/</t>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106048</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Akash.R</t>
+          <t>BRINDHA S</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>Brindha_S</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/Brindha_S/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>922525106050</t>
+          <t>922525106014</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>CHARUDESNA S</t>
+          <t>Akash.R</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>charu120108</t>
+          <t>AkashRajaram</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charu120108/</t>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>922525106051</t>
+          <t>922525106050</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CHARUNETHRA S</t>
+          <t>CHARUDESNA S</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>charunethra07</t>
+          <t>charu120108</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charunethra07/</t>
+          <t>https://leetcode.com/u/charu120108/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>922525106038</t>
+          <t>922525106051</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>BAVITHA T</t>
+          <t>CHARUNETHRA S</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>codewithakshaya</t>
+          <t>charunethra07</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya/</t>
+          <t>https://leetcode.com/u/charunethra07/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>922525106016</t>
+          <t>922525106038</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>AKSHAYA S</t>
+          <t>BAVITHA T</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>codewithakshaya78</t>
+          <t>codewithakshaya</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya78/</t>
+          <t>https://leetcode.com/u/codewithakshaya/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>922525106054</t>
+          <t>922525106016</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DAKSHINYA R</t>
+          <t>AKSHAYA S</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Dakshinya555</t>
+          <t>codewithakshaya78</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dakshinya555/</t>
+          <t>https://leetcode.com/u/codewithakshaya78/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>922525106057</t>
+          <t>922525106054</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DARSHAN V V</t>
+          <t>DAKSHINYA R</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Darshan_mainsh008</t>
+          <t>Dakshinya555</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106057</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>DARSHAN V V</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>Darshan_mainsh008</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>922525106040</t>
+          <t>922525106059</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>BHARANIDHARAN S</t>
+          <t>DEJASRI M</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Idvdnnsh577q</t>
+          <t>dejasri</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Idvdnnsh577q/</t>
+          <t>https://leetcode.com/u/dejasri/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106019</t>
+          <t>922525106013</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ANBARASU S</t>
+          <t>AJITH KUMAR M</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Anbarasu28122007</t>
+          <t>ajit_kumar_23</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -8027,17 +8027,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>922525106082</t>
+          <t>922525106099</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DINESH P</t>
+          <t>GOVARTHAN K S</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Dinesh_106082</t>
+          <t>922525106099</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8047,24 +8047,24 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dinesh_106082/</t>
+          <t>https://leetcode.com/u/922525106099/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>922525106082</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DINESHKUMAR P</t>
+          <t>DINESH P</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>Dinesh_106082</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8074,24 +8074,24 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106083/</t>
+          <t>https://leetcode.com/u/Dinesh_106082/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DINESHKUMAR V</t>
+          <t>DINESHKUMAR P</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8101,24 +8101,24 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106084/</t>
+          <t>https://leetcode.com/u/922525106083/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DIVYA ROJA R</t>
+          <t>DINESHKUMAR V</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8128,24 +8128,24 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106085/</t>
+          <t>https://leetcode.com/u/922525106084/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>922525106086</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DIVYA V</t>
+          <t>DIVYA ROJA R</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>princess-nk</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8155,24 +8155,24 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/princess-nk/</t>
+          <t>https://leetcode.com/u/922525106085/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>922525106086</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI G</t>
+          <t>DIVYA V</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>princess-nk</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8182,24 +8182,24 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106087/</t>
+          <t>https://leetcode.com/u/princess-nk/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI S</t>
+          <t>DIVYADHARSHINI G</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106088/</t>
+          <t>https://leetcode.com/u/922525106087/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DURAIMURUGAN K</t>
+          <t>DIVYADHARSHINI S</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106089/</t>
+          <t>https://leetcode.com/u/922525106088/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ELAKKIYA N</t>
+          <t>DURAIMURUGAN K</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8263,24 +8263,24 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106090/</t>
+          <t>https://leetcode.com/u/922525106089/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ELAVARASAN R</t>
+          <t>ELAKKIYA N</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8290,24 +8290,24 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106091/</t>
+          <t>https://leetcode.com/u/922525106090/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ELAVARASU P</t>
+          <t>ELAVARASAN R</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8317,24 +8317,24 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106092/</t>
+          <t>https://leetcode.com/u/922525106091/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>922525106094</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>GOKUL D</t>
+          <t>ELAVARASU P</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Gokul_tamilan_india</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
+          <t>https://leetcode.com/u/922525106092/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>922525106095</t>
+          <t>922525106094</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>GOMATHI R</t>
+          <t>GOKUL D</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>gomathi_0709</t>
+          <t>Gokul_tamilan_india</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/gomathi_0709/</t>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>922525106095</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>GOUTHAM R J</t>
+          <t>GOMATHI R</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>gomathi_0709</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8398,24 +8398,24 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106098/</t>
+          <t>https://leetcode.com/u/gomathi_0709/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>922525106099</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GOVARTHAN K S</t>
+          <t>GOUTHAM R J</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>GOVARTHANKS</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GOVARTHANKS/</t>
+          <t>https://leetcode.com/u/922525106098/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -1034,17 +1034,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
@@ -3680,17 +3680,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106168</t>
+          <t>922525106167</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LAVANYA V</t>
+          <t>LAKSHETHA V</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>lavilavanya</t>
+          <t>itz_lakshe</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lavilavanya/</t>
+          <t>https://leetcode.com/u/itz_lakshe/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106169</t>
+          <t>922525106168</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LINGESHWARAN K</t>
+          <t>LAVANYA V</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LING2007</t>
+          <t>lavilavanya</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LING2007/</t>
+          <t>https://leetcode.com/u/lavilavanya/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106170</t>
+          <t>922525106169</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LOGADHARSHINI T</t>
+          <t>LINGESHWARAN K</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LogadharshiniT</t>
+          <t>LING2007</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LogadharshiniT/</t>
+          <t>https://leetcode.com/u/LING2007/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106171</t>
+          <t>922525106170</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LOGASRI.A</t>
+          <t>LOGADHARSHINI T</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Loga07</t>
+          <t>LogadharshiniT</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Loga07/</t>
+          <t>https://leetcode.com/u/LogadharshiniT/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106172</t>
+          <t>922525106171</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LOGAVARDHAN M</t>
+          <t>LOGASRI.A</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>loga16</t>
+          <t>Loga07</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/loga16/</t>
+          <t>https://leetcode.com/u/Loga07/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106174</t>
+          <t>922525106172</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LOGESHWARAN K</t>
+          <t>LOGAVARDHAN M</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LOGESHWARAN2008</t>
+          <t>loga16</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
+          <t>https://leetcode.com/u/loga16/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>922525106175</t>
+          <t>922525106174</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LOHITH RAJ S</t>
+          <t>LOGESHWARAN K</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LOHITH012008</t>
+          <t>LOGESHWARAN2008</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH012008/</t>
+          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>922525106176</t>
+          <t>922525106175</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LOKRAJI R</t>
+          <t>LOHITH RAJ S</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LOKRAJI6793</t>
+          <t>LOHITH012008</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOKRAJI6793/</t>
+          <t>https://leetcode.com/u/LOHITH012008/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>922525106177</t>
+          <t>922525106176</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MADELIN JENITA M</t>
+          <t>LOKRAJI R</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jenita0206</t>
+          <t>LOKRAJI6793</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jenita0206/</t>
+          <t>https://leetcode.com/u/LOKRAJI6793/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>922525106179</t>
+          <t>922525106177</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MADHANKUMAR S</t>
+          <t>MADELIN JENITA M</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Madhankumar861053</t>
+          <t>jenita0206</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhankumar861053/</t>
+          <t>https://leetcode.com/u/jenita0206/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106179</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>MADHANKUMAR S</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>Madhankumar861053</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/Madhankumar861053/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922525106181</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MADHUMITHA B</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Madhumitha42</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhumitha42/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922525106182</t>
+          <t>922525106181</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Madhup Kishor G S</t>
+          <t>MADHUMITHA B</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Madhupkishor_20</t>
+          <t>Madhumitha42</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhupkishor_20/</t>
+          <t>https://leetcode.com/u/Madhumitha42/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106182</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>Madhup Kishor G S</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>Madhupkishor_20</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/Madhupkishor_20/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>922525106185</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI P</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>maha_lakh_20</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/maha_lakh_20/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106185</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MAHIBALAN .A</t>
+          <t>MAHALAKSHMI P</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>mahi2</t>
+          <t>maha_lakh_20</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi2/</t>
+          <t>https://leetcode.com/u/maha_lakh_20/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>922525106187</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MAHIN ABHISHEK VH</t>
+          <t>MAHIBALAN .A</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mahinabhishek0411</t>
+          <t>mahi2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4132,24 +4132,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
+          <t>https://leetcode.com/u/mahi2/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106187</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Manisha D</t>
+          <t>MAHIN ABHISHEK VH</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>Mahinabhishek0411</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4159,51 +4159,51 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>922525106190</t>
+          <t>922525106189</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MANOJ A</t>
+          <t>Manisha D</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Manoj_1319</t>
+          <t>manishaa_20</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Manoj_1319/</t>
+          <t>https://leetcode.com/u/manishaa_20/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>922525106191</t>
+          <t>922525106190</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Manoj Kumar V</t>
+          <t>MANOJ A</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>m____a____n____o____</t>
+          <t>Manoj_1319</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/m____a____n____o____/</t>
+          <t>https://leetcode.com/u/Manoj_1319/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>922525106193</t>
+          <t>922525106191</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MATHESHKUMAR S</t>
+          <t>Manoj Kumar V</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>mathesh25</t>
+          <t>m____a____n____o____</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mathesh25/</t>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>922525106194</t>
+          <t>922525106193</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MAYAKANNAN K</t>
+          <t>MATHESHKUMAR S</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mayakannan129</t>
+          <t>mathesh25</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayakannan129/</t>
+          <t>https://leetcode.com/u/mathesh25/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106194</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>MAYAKANNAN K</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Mayuka_M</t>
+          <t>Mayakannan129</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_M/</t>
+          <t>https://leetcode.com/u/Mayakannan129/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>922525106196</t>
+          <t>922525106195</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Milan D</t>
+          <t>MAYUKA M</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>milan190308</t>
+          <t>Mayuka_M</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/milan190308/</t>
+          <t>https://leetcode.com/u/Mayuka_M/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>922525106200</t>
+          <t>922525106196</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MONISHA R</t>
+          <t>Milan D</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>itsmoni</t>
+          <t>milan190308</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmoni/</t>
+          <t>https://leetcode.com/u/milan190308/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>922525106201</t>
+          <t>922525106200</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MONISHA V</t>
+          <t>MONISHA R</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Monishav2007</t>
+          <t>itsmoni</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Monishav2007/</t>
+          <t>https://leetcode.com/u/itsmoni/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>922525106202</t>
+          <t>922525106201</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Morrish D</t>
+          <t>MONISHA V</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>morrishd</t>
+          <t>Monishav2007</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/morrishd/</t>
+          <t>https://leetcode.com/u/Monishav2007/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>922525106203</t>
+          <t>922525106202</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MOULEESHWARI B</t>
+          <t>Morrish D</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mouleeshwari2008</t>
+          <t>morrishd</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
+          <t>https://leetcode.com/u/morrishd/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>922525106204</t>
+          <t>922525106203</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MOUSHMI P N</t>
+          <t>MOULEESHWARI B</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Moushmi_20</t>
+          <t>Mouleeshwari2008</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4456,34 +4456,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Moushmi_20/</t>
+          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>922525106106</t>
+          <t>922525106204</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>GOWTHAMAN N</t>
+          <t>MOUSHMI P N</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>92252510610</t>
+          <t>Moushmi_20</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/92252510610/</t>
+          <t>https://leetcode.com/u/Moushmi_20/</t>
         </is>
       </c>
     </row>
@@ -8054,17 +8054,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>922525106082</t>
+          <t>922525106106</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DINESH P</t>
+          <t>GOWTHAMAN N</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Dinesh_106082</t>
+          <t>922525106106</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8074,24 +8074,24 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dinesh_106082/</t>
+          <t>https://leetcode.com/u/922525106106/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>922525106082</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DINESHKUMAR P</t>
+          <t>DINESH P</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>Dinesh_106082</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8101,24 +8101,24 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106083/</t>
+          <t>https://leetcode.com/u/Dinesh_106082/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DINESHKUMAR V</t>
+          <t>DINESHKUMAR P</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8128,24 +8128,24 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106084/</t>
+          <t>https://leetcode.com/u/922525106083/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DIVYA ROJA R</t>
+          <t>DINESHKUMAR V</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8155,24 +8155,24 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106085/</t>
+          <t>https://leetcode.com/u/922525106084/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>922525106086</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DIVYA V</t>
+          <t>DIVYA ROJA R</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>princess-nk</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8182,24 +8182,24 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/princess-nk/</t>
+          <t>https://leetcode.com/u/922525106085/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>922525106086</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI G</t>
+          <t>DIVYA V</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>princess-nk</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106087/</t>
+          <t>https://leetcode.com/u/princess-nk/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI S</t>
+          <t>DIVYADHARSHINI G</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106088/</t>
+          <t>https://leetcode.com/u/922525106087/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DURAIMURUGAN K</t>
+          <t>DIVYADHARSHINI S</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8263,24 +8263,24 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106089/</t>
+          <t>https://leetcode.com/u/922525106088/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ELAKKIYA N</t>
+          <t>DURAIMURUGAN K</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8290,24 +8290,24 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106090/</t>
+          <t>https://leetcode.com/u/922525106089/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ELAVARASAN R</t>
+          <t>ELAKKIYA N</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8317,24 +8317,24 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106091/</t>
+          <t>https://leetcode.com/u/922525106090/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ELAVARASU P</t>
+          <t>ELAVARASAN R</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106092/</t>
+          <t>https://leetcode.com/u/922525106091/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>922525106094</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>GOKUL D</t>
+          <t>ELAVARASU P</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Gokul_tamilan_india</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
+          <t>https://leetcode.com/u/922525106092/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>922525106095</t>
+          <t>922525106094</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>GOMATHI R</t>
+          <t>GOKUL D</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>gomathi_0709</t>
+          <t>Gokul_tamilan_india</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8398,24 +8398,24 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/gomathi_0709/</t>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>922525106095</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GOUTHAM R J</t>
+          <t>GOMATHI R</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>gomathi_0709</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8425,24 +8425,24 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106098/</t>
+          <t>https://leetcode.com/u/gomathi_0709/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>922525106100</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>GOWRIKA K P</t>
+          <t>GOUTHAM R J</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>922525106100</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8452,24 +8452,24 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106100/</t>
+          <t>https://leetcode.com/u/922525106098/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>922525106101</t>
+          <t>922525106100</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>GOWRISANKAR S</t>
+          <t>GOWRIKA K P</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>922524106101</t>
+          <t>922525106100</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8479,24 +8479,24 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922524106101/</t>
+          <t>https://leetcode.com/u/922525106100/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>922525106102</t>
+          <t>922525106101</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>GOWSICK S</t>
+          <t>GOWRISANKAR S</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>922525106106</t>
+          <t>922524106101</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106106/</t>
+          <t>https://leetcode.com/u/922524106101/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>922525106103</t>
+          <t>922525106102</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>GOWTHAM M</t>
+          <t>GOWSICK S</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>922525106103</t>
+          <t>922525106106</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106103/</t>
+          <t>https://leetcode.com/u/922525106106/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>922525106104</t>
+          <t>922525106103</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>GOWTHAM R</t>
+          <t>GOWTHAM M</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>922525106104</t>
+          <t>922525106103</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106104/</t>
+          <t>https://leetcode.com/u/922525106103/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>922525106105</t>
+          <t>922525106104</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>GOWTHAM S</t>
+          <t>GOWTHAM R</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Gowtham_080</t>
+          <t>922525106104</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gowtham_080/</t>
+          <t>https://leetcode.com/u/922525106104/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>922525106107</t>
+          <t>922525106105</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>GUNA SHREE V</t>
+          <t>GOWTHAM S</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Gunashree20</t>
+          <t>Gowtham_080</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gunashree20/</t>
+          <t>https://leetcode.com/u/Gowtham_080/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>922525106108</t>
+          <t>922525106107</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>GURUSARAN R</t>
+          <t>GUNA SHREE V</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>922525106108</t>
+          <t>Gunashree20</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106108/</t>
+          <t>https://leetcode.com/u/Gunashree20/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>922525106109</t>
+          <t>922525106108</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>HANSHIKAVARSA K S</t>
+          <t>GURUSARAN R</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>922525106109</t>
+          <t>922525106108</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106109/</t>
+          <t>https://leetcode.com/u/922525106108/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>922525106110</t>
+          <t>922525106109</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>HARI HARAN R</t>
+          <t>HANSHIKAVARSA K S</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>922525106110</t>
+          <t>922525106109</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106110/</t>
+          <t>https://leetcode.com/u/922525106109/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>922525106111</t>
+          <t>922525106110</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>HARIS S</t>
+          <t>HARI HARAN R</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>922525106111</t>
+          <t>922525106110</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106111/</t>
+          <t>https://leetcode.com/u/922525106110/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>922525106112</t>
+          <t>922525106111</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HARINI S</t>
+          <t>HARIS S</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>922525106112</t>
+          <t>922525106111</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106112/</t>
+          <t>https://leetcode.com/u/922525106111/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>922525106113</t>
+          <t>922525106112</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HARIS M</t>
+          <t>HARINI S</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>922525106113</t>
+          <t>922525106112</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106113/</t>
+          <t>https://leetcode.com/u/922525106112/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>922525106114</t>
+          <t>922525106113</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>HARIS RAGAVENDAR A</t>
+          <t>HARIS M</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>922525106114</t>
+          <t>922525106113</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106114/</t>
+          <t>https://leetcode.com/u/922525106113/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>922525106115</t>
+          <t>922525106114</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>HARISH D</t>
+          <t>HARIS RAGAVENDAR A</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>922525106115</t>
+          <t>922525106114</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106115/</t>
+          <t>https://leetcode.com/u/922525106114/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>922525106116</t>
+          <t>922525106115</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>HARISH M S</t>
+          <t>HARISH D</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>922525106116</t>
+          <t>922525106115</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106116/</t>
+          <t>https://leetcode.com/u/922525106115/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>922525106117</t>
+          <t>922525106116</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>HARISH P</t>
+          <t>HARISH M S</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>922525106117</t>
+          <t>922525106116</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8884,24 +8884,24 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106117/</t>
+          <t>https://leetcode.com/u/922525106116/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>922525106118</t>
+          <t>922525106117</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>HARISHANKAR R</t>
+          <t>HARISH P</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>922525106118</t>
+          <t>922525106117</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106118/</t>
+          <t>https://leetcode.com/u/922525106117/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>922525106119</t>
+          <t>922525106118</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>HAVISHMATHI S</t>
+          <t>HARISHANKAR R</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HAVISHMATHIS</t>
+          <t>922525106118</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
+          <t>https://leetcode.com/u/922525106118/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>922525106120</t>
+          <t>922525106119</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>HEMAA SRI A</t>
+          <t>HAVISHMATHI S</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>922525106120</t>
+          <t>HAVISHMATHIS</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8965,24 +8965,24 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106120/</t>
+          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>922525106120</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>HEMAVARSHINI S</t>
+          <t>HEMAA SRI A</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>922525106120</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8992,24 +8992,24 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106121/</t>
+          <t>https://leetcode.com/u/922525106120/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>HIRESH K</t>
+          <t>HEMAVARSHINI S</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9019,24 +9019,24 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106122/</t>
+          <t>https://leetcode.com/u/922525106121/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>INBNATHAN S</t>
+          <t>HIRESH K</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9046,24 +9046,24 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106123/</t>
+          <t>https://leetcode.com/u/922525106122/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>INDHIRAJITH K</t>
+          <t>INBNATHAN S</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9073,24 +9073,24 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106124/</t>
+          <t>https://leetcode.com/u/922525106123/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>INDHIRAJITH K</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9100,24 +9100,24 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106125/</t>
+          <t>https://leetcode.com/u/922525106124/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>922525106126</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>JANA S</t>
+          <t>JAI GANESH I</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>922525106126</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9127,51 +9127,51 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106126/</t>
+          <t>https://leetcode.com/u/922525106125/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>922525106127</t>
+          <t>922525106126</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>JANANI A</t>
+          <t>JANA S</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>janani_asohkan</t>
+          <t>922525106126</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/janani_asohkan/</t>
+          <t>https://leetcode.com/u/922525106126/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>922525106128</t>
+          <t>922525106127</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>JASHVANTH J S</t>
+          <t>JANANI A</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>jashvanth2007</t>
+          <t>janani_asohkan</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9181,24 +9181,24 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jashvanth2007/</t>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>922525106130</t>
+          <t>922525106128</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>JAYASAKTHI V</t>
+          <t>JASHVANTH J S</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>jayasakthi_25</t>
+          <t>jashvanth2007</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9208,24 +9208,24 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jayasakthi_25/</t>
+          <t>https://leetcode.com/u/jashvanth2007/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>922525106132</t>
+          <t>922525106130</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Jeevan bala G</t>
+          <t>JAYASAKTHI V</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>jeevanbala142008</t>
+          <t>jayasakthi_25</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9235,24 +9235,24 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanbala142008/</t>
+          <t>https://leetcode.com/u/jayasakthi_25/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>922525106133</t>
+          <t>922525106132</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>JEEVADHARSHAN R R</t>
+          <t>Jeevan bala G</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>dharshanjeeva</t>
+          <t>jeevanbala142008</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9262,24 +9262,24 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshanjeeva/</t>
+          <t>https://leetcode.com/u/jeevanbala142008/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>922525106134</t>
+          <t>922525106133</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>JEEVANAA S</t>
+          <t>JEEVADHARSHAN R R</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>jeevanaa_174_</t>
+          <t>dharshanjeeva</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9289,24 +9289,24 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanaa_174_/</t>
+          <t>https://leetcode.com/u/dharshanjeeva/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>922525106135</t>
+          <t>922525106134</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>JERSHITH J S</t>
+          <t>JEEVANAA S</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Jerry2008</t>
+          <t>jeevanaa_174_</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jerry2008/</t>
+          <t>https://leetcode.com/u/jeevanaa_174_/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>922525106136</t>
+          <t>922525106135</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>JOSHITHA KANNAN SUDHA</t>
+          <t>JERSHITH J S</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Joshi_666</t>
+          <t>Jerry2008</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9343,24 +9343,24 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Joshi_666/</t>
+          <t>https://leetcode.com/u/Jerry2008/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>922525106137</t>
+          <t>922525106136</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Jothi harshan D K</t>
+          <t>JOSHITHA KANNAN SUDHA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Jothiharshan16</t>
+          <t>Joshi_666</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9370,24 +9370,24 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothiharshan16/</t>
+          <t>https://leetcode.com/u/Joshi_666/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>922525106138</t>
+          <t>922525106137</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>JOTHISHA K S</t>
+          <t>Jothi harshan D K</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Jothi-</t>
+          <t>Jothiharshan16</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothi-/</t>
+          <t>https://leetcode.com/u/Jothiharshan16/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>922525106139</t>
+          <t>922525106138</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>KAMALINI G</t>
+          <t>JOTHISHA K S</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>_kamalini_</t>
+          <t>Jothi-</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9424,24 +9424,24 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_kamalini_/</t>
+          <t>https://leetcode.com/u/Jothi-/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>922525106140</t>
+          <t>922525106139</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>KANISHKA A R</t>
+          <t>KAMALINI G</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>26kanishka</t>
+          <t>_kamalini_</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9451,24 +9451,24 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/26kanishka/</t>
+          <t>https://leetcode.com/u/_kamalini_/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>922525106142</t>
+          <t>922525106140</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>KANITHRA R</t>
+          <t>KANISHKA A R</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>kanithraakila</t>
+          <t>26kanishka</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9478,24 +9478,24 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanithraakila/</t>
+          <t>https://leetcode.com/u/26kanishka/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>922525106143</t>
+          <t>922525106142</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>KARISHMA M</t>
+          <t>KANITHRA R</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Karishma_m_08</t>
+          <t>kanithraakila</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karishma_m_08/</t>
+          <t>https://leetcode.com/u/kanithraakila/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106143</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>KARISHMA M</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>Karishma_m_08</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9532,24 +9532,24 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/Karishma_m_08/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>922525106145</t>
+          <t>922525106144</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>KARSHANA SRI V</t>
+          <t>KARMUKILAN J</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>karshana_234</t>
+          <t>karmukilan567</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9559,24 +9559,24 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karshana_234/</t>
+          <t>https://leetcode.com/u/karmukilan567/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>922525106146</t>
+          <t>922525106145</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>KARTHIKA K</t>
+          <t>KARSHANA SRI V</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Karthi270827</t>
+          <t>karshana_234</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9586,24 +9586,24 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karthi270827/</t>
+          <t>https://leetcode.com/u/karshana_234/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>922525106148</t>
+          <t>922525106146</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>KAVIMALAR A</t>
+          <t>KARTHIKA K</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>kavimalar08</t>
+          <t>Karthi270827</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9613,24 +9613,24 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavimalar08/</t>
+          <t>https://leetcode.com/u/Karthi270827/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>922525106149</t>
+          <t>922525106148</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>KAVIN KUMAR S</t>
+          <t>KAVIMALAR A</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>KAVIN__26</t>
+          <t>kavimalar08</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9640,78 +9640,78 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVIN__26/</t>
+          <t>https://leetcode.com/u/kavimalar08/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>922525106012</t>
+          <t>922525106149</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>AJAYKUMAR A L</t>
+          <t>KAVIN KUMAR S</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>AjaykumarAL</t>
+          <t>KAVIN__26</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AjaykumarAL/</t>
+          <t>https://leetcode.com/u/KAVIN__26/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>922525106150</t>
+          <t>922525106012</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>KAVINKUMAR M</t>
+          <t>AJAYKUMAR A L</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>kavinleet</t>
+          <t>AjaykumarAL</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavinleet/</t>
+          <t>https://leetcode.com/u/AjaykumarAL/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>922525106151</t>
+          <t>922525106150</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>KAVIPRIYA J</t>
+          <t>KAVINKUMAR M</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>_kavipriya_16</t>
+          <t>kavinleet</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9721,24 +9721,24 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_kavipriya_16/</t>
+          <t>https://leetcode.com/u/kavinleet/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>922525106152</t>
+          <t>922525106151</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>KAVIPRIYA R</t>
+          <t>KAVIPRIYA J</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>KAVI_RAVI</t>
+          <t>_kavipriya_16</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9748,24 +9748,24 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+          <t>https://leetcode.com/u/_kavipriya_16/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>922525106153</t>
+          <t>922525106152</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>KAVIYARASU K</t>
+          <t>KAVIPRIYA R</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>kavi12d</t>
+          <t>KAVI_RAVI</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9775,24 +9775,24 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavi12d/</t>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>922525106154</t>
+          <t>922525106153</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>KAVYA A</t>
+          <t>KAVIYARASU K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>itzz__kavya02</t>
+          <t>kavi12d</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9802,24 +9802,24 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itzz__kavya02/</t>
+          <t>https://leetcode.com/u/kavi12d/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>922525106155</t>
+          <t>922525106154</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>KAYALVIZHI S</t>
+          <t>KAVYA A</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>27kayalvizhi</t>
+          <t>itzz__kavya02</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9829,24 +9829,24 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/27kayalvizhi/</t>
+          <t>https://leetcode.com/u/itzz__kavya02/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106155</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>KAYALVIZHI S</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>keerthana_19selvam</t>
+          <t>27kayalvizhi</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9856,24 +9856,24 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/keerthana_19selvam/</t>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>922525106157</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>KESAVINI M</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>KESAVINI892</t>
+          <t>keerthana_19selvam</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9883,24 +9883,24 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KESAVINI892/</t>
+          <t>https://leetcode.com/u/keerthana_19selvam/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>922525106158</t>
+          <t>922525106157</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>KIRUTHIKA S</t>
+          <t>KESAVINI M</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>kiruthika_selvanathan05092007</t>
+          <t>KESAVINI892</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9910,24 +9910,24 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
+          <t>https://leetcode.com/u/KESAVINI892/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106158</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>KIRUTHIKA S</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>kohul_v</t>
+          <t>kiruthika_selvanathan05092007</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kohul_v/</t>
+          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>922525106161</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>KOWSHIK M</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>kowshikm23</t>
+          <t>kohul_v</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9964,24 +9964,24 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshikm23/</t>
+          <t>https://leetcode.com/u/kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>922525106162</t>
+          <t>922525106161</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>KOWSHIK R</t>
+          <t>KOWSHIK M</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>kowshik_rk_</t>
+          <t>kowshikm23</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9991,24 +9991,24 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshik_rk_/</t>
+          <t>https://leetcode.com/u/kowshikm23/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>922525106163</t>
+          <t>922525106162</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>KOWSHIKA B</t>
+          <t>KOWSHIK R</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Kowshika08</t>
+          <t>kowshik_rk_</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10018,24 +10018,24 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kowshika08/</t>
+          <t>https://leetcode.com/u/kowshik_rk_/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>922525106164</t>
+          <t>922525106163</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>KOWSHIKA M S</t>
+          <t>KOWSHIKA B</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>kowshika_moorthi</t>
+          <t>Kowshika08</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10045,24 +10045,24 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+          <t>https://leetcode.com/u/Kowshika08/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>922525106165</t>
+          <t>922525106164</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>KOWSHIKAN P</t>
+          <t>KOWSHIKA M S</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>KOWSHIKAN-PALANISAMY</t>
+          <t>kowshika_moorthi</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10072,24 +10072,24 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>922525106166</t>
+          <t>922525106165</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>KRISH R</t>
+          <t>KOWSHIKAN P</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>krish-2007</t>
+          <t>KOWSHIKAN-PALANISAMY</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/krish-2007/</t>
+          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>922525106167</t>
+          <t>922525106166</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>LAKSHETHA V</t>
+          <t>KRISH R</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>itz_lakshe</t>
+          <t>krish-2007</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_lakshe/</t>
+          <t>https://leetcode.com/u/krish-2007/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -8999,17 +8999,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>HEMAVARSHINI S</t>
+          <t>JAI GANESH I</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>Jai_Ganesh_I</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9019,24 +9019,24 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106121/</t>
+          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>HIRESH K</t>
+          <t>HEMAVARSHINI S</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9046,24 +9046,24 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106122/</t>
+          <t>https://leetcode.com/u/922525106121/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>INBNATHAN S</t>
+          <t>HIRESH K</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9073,24 +9073,24 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106123/</t>
+          <t>https://leetcode.com/u/922525106122/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>INDHIRAJITH K</t>
+          <t>INBNATHAN S</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9100,24 +9100,24 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106124/</t>
+          <t>https://leetcode.com/u/922525106123/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>INDHIRAJITH K</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106125/</t>
+          <t>https://leetcode.com/u/922525106124/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -845,17 +845,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
@@ -1061,17 +1061,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
@@ -1169,17 +1169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
@@ -3680,17 +3680,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106167</t>
+          <t>922525106166</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LAKSHETHA V</t>
+          <t>KRISH R</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>itz_lakshe</t>
+          <t>krish-2007</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_lakshe/</t>
+          <t>https://leetcode.com/u/krish-2007/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106168</t>
+          <t>922525106167</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LAVANYA V</t>
+          <t>LAKSHETHA V</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>lavilavanya</t>
+          <t>itz_lakshe</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lavilavanya/</t>
+          <t>https://leetcode.com/u/itz_lakshe/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106169</t>
+          <t>922525106168</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LINGESHWARAN K</t>
+          <t>LAVANYA V</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LING2007</t>
+          <t>lavilavanya</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LING2007/</t>
+          <t>https://leetcode.com/u/lavilavanya/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106170</t>
+          <t>922525106169</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LOGADHARSHINI T</t>
+          <t>LINGESHWARAN K</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LogadharshiniT</t>
+          <t>LING2007</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LogadharshiniT/</t>
+          <t>https://leetcode.com/u/LING2007/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106171</t>
+          <t>922525106170</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LOGASRI.A</t>
+          <t>LOGADHARSHINI T</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Loga07</t>
+          <t>LogadharshiniT</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Loga07/</t>
+          <t>https://leetcode.com/u/LogadharshiniT/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106172</t>
+          <t>922525106171</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LOGAVARDHAN M</t>
+          <t>LOGASRI.A</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>loga16</t>
+          <t>Loga07</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/loga16/</t>
+          <t>https://leetcode.com/u/Loga07/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>922525106174</t>
+          <t>922525106172</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LOGESHWARAN K</t>
+          <t>LOGAVARDHAN M</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LOGESHWARAN2008</t>
+          <t>loga16</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
+          <t>https://leetcode.com/u/loga16/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>922525106175</t>
+          <t>922525106174</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LOHITH RAJ S</t>
+          <t>LOGESHWARAN K</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LOHITH012008</t>
+          <t>LOGESHWARAN2008</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH012008/</t>
+          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>922525106176</t>
+          <t>922525106175</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LOKRAJI R</t>
+          <t>LOHITH RAJ S</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LOKRAJI6793</t>
+          <t>LOHITH012008</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOKRAJI6793/</t>
+          <t>https://leetcode.com/u/LOHITH012008/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>922525106177</t>
+          <t>922525106176</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MADELIN JENITA M</t>
+          <t>LOKRAJI R</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jenita0206</t>
+          <t>LOKRAJI6793</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jenita0206/</t>
+          <t>https://leetcode.com/u/LOKRAJI6793/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>922525106179</t>
+          <t>922525106177</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MADHANKUMAR S</t>
+          <t>MADELIN JENITA M</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Madhankumar861053</t>
+          <t>jenita0206</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhankumar861053/</t>
+          <t>https://leetcode.com/u/jenita0206/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106179</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>MADHANKUMAR S</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>Madhankumar861053</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/Madhankumar861053/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922525106181</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MADHUMITHA B</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Madhumitha42</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhumitha42/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>922525106182</t>
+          <t>922525106181</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Madhup Kishor G S</t>
+          <t>MADHUMITHA B</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Madhupkishor_20</t>
+          <t>Madhumitha42</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhupkishor_20/</t>
+          <t>https://leetcode.com/u/Madhumitha42/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106182</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>Madhup Kishor G S</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>Madhupkishor_20</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/Madhupkishor_20/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>922525106185</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI P</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>maha_lakh_20</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/maha_lakh_20/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106185</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MAHIBALAN .A</t>
+          <t>MAHALAKSHMI P</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>mahi2</t>
+          <t>maha_lakh_20</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi2/</t>
+          <t>https://leetcode.com/u/maha_lakh_20/</t>
         </is>
       </c>
     </row>
@@ -9809,17 +9809,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>922525106154</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>KAVYA A</t>
+          <t>MAHIBALAN .A</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>itzz__kavya02</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9829,24 +9829,24 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itzz__kavya02/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>922525106155</t>
+          <t>922525106154</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>KAYALVIZHI S</t>
+          <t>KAVYA A</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>27kayalvizhi</t>
+          <t>itzz__kavya02</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9856,24 +9856,24 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/27kayalvizhi/</t>
+          <t>https://leetcode.com/u/itzz__kavya02/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106155</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>KAYALVIZHI S</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>keerthana_19selvam</t>
+          <t>27kayalvizhi</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9883,24 +9883,24 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/keerthana_19selvam/</t>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>922525106157</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>KESAVINI M</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>KESAVINI892</t>
+          <t>keerthana_19selvam</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9910,24 +9910,24 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KESAVINI892/</t>
+          <t>https://leetcode.com/u/keerthana_19selvam/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>922525106158</t>
+          <t>922525106157</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>KIRUTHIKA S</t>
+          <t>KESAVINI M</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>kiruthika_selvanathan05092007</t>
+          <t>KESAVINI892</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
+          <t>https://leetcode.com/u/KESAVINI892/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106158</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>KIRUTHIKA S</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>kohul_v</t>
+          <t>kiruthika_selvanathan05092007</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9964,24 +9964,24 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kohul_v/</t>
+          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>922525106161</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>KOWSHIK M</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>kowshikm23</t>
+          <t>kohul_v</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9991,24 +9991,24 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshikm23/</t>
+          <t>https://leetcode.com/u/kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>922525106162</t>
+          <t>922525106161</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>KOWSHIK R</t>
+          <t>KOWSHIK M</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>kowshik_rk_</t>
+          <t>kowshikm23</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10018,24 +10018,24 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshik_rk_/</t>
+          <t>https://leetcode.com/u/kowshikm23/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>922525106163</t>
+          <t>922525106162</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>KOWSHIKA B</t>
+          <t>KOWSHIK R</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Kowshika08</t>
+          <t>kowshik_rk_</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10045,24 +10045,24 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kowshika08/</t>
+          <t>https://leetcode.com/u/kowshik_rk_/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>922525106164</t>
+          <t>922525106163</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>KOWSHIKA M S</t>
+          <t>KOWSHIKA B</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>kowshika_moorthi</t>
+          <t>Kowshika08</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10072,24 +10072,24 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+          <t>https://leetcode.com/u/Kowshika08/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>922525106165</t>
+          <t>922525106164</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>KOWSHIKAN P</t>
+          <t>KOWSHIKA M S</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>KOWSHIKAN-PALANISAMY</t>
+          <t>kowshika_moorthi</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>922525106166</t>
+          <t>922525106165</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>KRISH R</t>
+          <t>KOWSHIKAN P</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>krish-2007</t>
+          <t>KOWSHIKAN-PALANISAMY</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/krish-2007/</t>
+          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
@@ -6839,17 +6839,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>922525106251</t>
+          <t>922525106252</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>RETHANYA S</t>
+          <t>RETHISH</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>rethanya38</t>
+          <t>Rethish_R</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6859,24 +6859,24 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rethanya38/</t>
+          <t>https://leetcode.com/u/Rethish_R/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>922525106252</t>
+          <t>922525106251</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>RETHISH</t>
+          <t>RETHANYA S</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Rethish_R</t>
+          <t>rethanya38</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rethish_R/</t>
+          <t>https://leetcode.com/u/rethanya38/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
@@ -1871,17 +1871,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>_swathi_3366</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
         </is>
       </c>
     </row>
@@ -2411,17 +2411,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
@@ -3005,17 +3005,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
@@ -6002,17 +6002,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106013</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AJITH KUMAR M</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>ajit_kumar_23</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106013</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AJITH KUMAR M</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ajit_kumar_23</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>THIRINESHKUMAR0608</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
@@ -3140,17 +3140,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$364</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E363"/>
+  <dimension ref="A1:E364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>THIRINESHKUMAR0608</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>_swathi_3366</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>_swathi_3366</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>THIRINESHKUMAR0608</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
@@ -10238,8 +10238,35 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>922525106141</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>KANISHKUMAR M</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>kanishkumar2008</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kanishkumar2008/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E363"/>
+  <autoFilter ref="A1:E364"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$365</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E364"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>_swathi_3366</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>THIRINESHKUMAR0608</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>_swathi_3366</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>THIRINESHKUMAR0608</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
@@ -5975,17 +5975,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
@@ -10265,8 +10265,35 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>922525106159</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>KISHOREKUMAR B</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Kishore9225</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Kishore9225/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E364"/>
+  <autoFilter ref="A1:E365"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$366</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>_swathi_3366</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>THIRINESHKUMAR0608</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>_swathi_3366</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>THIRINESHKUMAR0608</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
@@ -10292,8 +10292,35 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>922525106212</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>NETHRA S</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Nethra777</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nethra777/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E365"/>
+  <autoFilter ref="A1:E366"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -818,17 +818,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SABAREESH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
@@ -3005,17 +3005,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
@@ -3221,17 +3221,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$367</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:E367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10319,8 +10319,35 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>922525106277</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SANJEVI P</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>sanjevi007</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjevi007/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E366"/>
+  <autoFilter ref="A1:E367"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$368</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E367"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SABAREESH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SABAREESH</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>THIRINESHKUMAR0608</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>_swathi_3366</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>_swathi_3366</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>THIRINESHKUMAR0608</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
@@ -3302,17 +3302,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
@@ -5975,17 +5975,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
@@ -10346,8 +10346,35 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>922525106379</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>ARUN KUMAR</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>arunkumar1004</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arunkumar1004/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E367"/>
+  <autoFilter ref="A1:E368"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$369</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SABAREESH</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SABAREESH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>THIRINESHKUMAR0608</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>_swathi_3366</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>THIRINESHKUMAR0608</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>_swathi_3366</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
@@ -5975,17 +5975,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
@@ -10373,8 +10373,35 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>922525106255</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>RITHIK I</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Rithik2008</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithik2008/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E368"/>
+  <autoFilter ref="A1:E369"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>Sivadharshini D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>dharshinideivasigamani</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/dharshinideivasigamani/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SABAREESH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
@@ -845,17 +845,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>sivanesh D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SABAREESH</t>
+          <t>Sanjay U</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>santhosh s</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>santhoshsathya260</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/santhoshsathya260/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>Sarveswaran R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>Rithik P</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>Rithish R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>sahana.v</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>sakthivel. M</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106293</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>saswin D</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SASHMIKA P</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
@@ -1871,17 +1871,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>THIRINESHKUMAR0608</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>_swathi_3366</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>sujith45</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/sujith45/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>_swathi_3366</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>THIRINESHKUMAR0608</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SANJAYAN</t>
+          <t>Sanjayan S</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SATHANA SRI S K</t>
+          <t>Sathana Sri S K</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SANTHOSH SHAI SIRIL</t>
+          <t>SHANTHOSH SHAI SIRIL R</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5975,17 +5975,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>922525106013</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AJITH KUMAR M</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ajit_kumar_23</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>922525106019</t>
+          <t>922525106013</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ANBARASU S</t>
+          <t>AJITH KUMAR M</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Anbarasu28122007</t>
+          <t>ajit_kumar_23</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>922525106020</t>
+          <t>922525106019</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ANJITHAA N</t>
+          <t>ANBARASU S</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Anjithaa2006</t>
+          <t>Anbarasu28122007</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106020</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANJITHAA N</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>Anjithaa2006</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>922525106008</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>AHELESH G S</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/B/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>922525106037</t>
+          <t>922525106008</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>BARANITHARAN V</t>
+          <t>AHELESH G S</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>barani_7</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/barani_7/</t>
+          <t>https://leetcode.com/u/B/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>922525106039</t>
+          <t>922525106037</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>BENOV NAVIN V</t>
+          <t>BARANITHARAN V</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Benov_18</t>
+          <t>barani_7</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Benov_18/</t>
+          <t>https://leetcode.com/u/barani_7/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>922525106044</t>
+          <t>922525106039</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Bhavan bala N</t>
+          <t>BENOV NAVIN V</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BhavanBala</t>
+          <t>Benov_18</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BhavanBala/</t>
+          <t>https://leetcode.com/u/Benov_18/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>922525106041</t>
+          <t>922525106044</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>BHARATH KUMAR E</t>
+          <t>Bhavan bala N</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BK5226221</t>
+          <t>BhavanBala</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BK5226221/</t>
+          <t>https://leetcode.com/u/BhavanBala/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>922525106045</t>
+          <t>922525106041</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>BOOBASE R</t>
+          <t>BHARATH KUMAR E</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Boobase</t>
+          <t>BK5226221</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Boobase/</t>
+          <t>https://leetcode.com/u/BK5226221/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>922525106046</t>
+          <t>922525106045</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>BOOMIKA T</t>
+          <t>BOOBASE R</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>boomikat123</t>
+          <t>Boobase</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/boomikat123/</t>
+          <t>https://leetcode.com/u/Boobase/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106046</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>BOOMIKA T</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>boomikat123</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/boomikat123/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>922525106048</t>
+          <t>922525106047</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>BRINDHA S</t>
+          <t>BOSVIYA P</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Brindha_S</t>
+          <t>BosviyaBSV</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Brindha_S/</t>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106048</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Akash.R</t>
+          <t>BRINDHA S</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>Brindha_S</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/Brindha_S/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>922525106050</t>
+          <t>922525106014</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CHARUDESNA S</t>
+          <t>Akash.R</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>charu120108</t>
+          <t>AkashRajaram</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charu120108/</t>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>922525106051</t>
+          <t>922525106050</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CHARUNETHRA S</t>
+          <t>CHARUDESNA S</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>charunethra07</t>
+          <t>charu120108</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charunethra07/</t>
+          <t>https://leetcode.com/u/charu120108/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>922525106038</t>
+          <t>922525106051</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>BAVITHA T</t>
+          <t>CHARUNETHRA S</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>codewithakshaya</t>
+          <t>charunethra07</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya/</t>
+          <t>https://leetcode.com/u/charunethra07/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>922525106016</t>
+          <t>922525106038</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>AKSHAYA S</t>
+          <t>BAVITHA T</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>codewithakshaya78</t>
+          <t>codewithakshaya</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya78/</t>
+          <t>https://leetcode.com/u/codewithakshaya/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>922525106054</t>
+          <t>922525106016</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DAKSHINYA R</t>
+          <t>AKSHAYA S</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Dakshinya555</t>
+          <t>codewithakshaya78</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dakshinya555/</t>
+          <t>https://leetcode.com/u/codewithakshaya78/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>922525106057</t>
+          <t>922525106054</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DARSHAN V V</t>
+          <t>DAKSHINYA R</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Darshan_mainsh008</t>
+          <t>Dakshinya555</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106057</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>DARSHAN V V</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>Darshan_mainsh008</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>922525106025</t>
+          <t>922525106059</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ARSATHA BEGAM M S</t>
+          <t>DEJASRI M</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>jakabesj</t>
+          <t>dejasri</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6616,78 +6616,78 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jakabesj/</t>
+          <t>https://leetcode.com/u/dejasri/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>922525106129</t>
+          <t>922525106025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JASVANTHRAM SP</t>
+          <t>ARSATHA BEGAM M S</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>jasvanthram</t>
+          <t>jakabesj</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jasvanthram/</t>
+          <t>https://leetcode.com/u/jakabesj/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>922525106010</t>
+          <t>922525106129</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>AJAIRAJAN SR</t>
+          <t>JASVANTHRAM SP</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>UJw4zUNnJJ</t>
+          <t>jasvanthram</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/UJw4zUNnJJ/</t>
+          <t>https://leetcode.com/u/jasvanthram/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>922525106026</t>
+          <t>922525106010</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ARUL S.T.</t>
+          <t>AJAIRAJAN SR</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>S_T_Arul</t>
+          <t>UJw4zUNnJJ</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6697,78 +6697,78 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/S_T_Arul/</t>
+          <t>https://leetcode.com/u/UJw4zUNnJJ/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>922525106076</t>
+          <t>922525106026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DHARSINI V S</t>
+          <t>ARUL S.T.</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>vsdharsini</t>
+          <t>S_T_Arul</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vsdharsini/</t>
+          <t>https://leetcode.com/u/S_T_Arul/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>922525106198</t>
+          <t>922525106076</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MOHAMMED ABUTHARIK S</t>
+          <t>DHARSINI V S</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>tharik25</t>
+          <t>vsdharsini</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/tharik25/</t>
+          <t>https://leetcode.com/u/vsdharsini/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>922525106199</t>
+          <t>922525106198</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MONISH S</t>
+          <t>MOHAMMED ABUTHARIK S</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>smonish777</t>
+          <t>tharik25</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6778,24 +6778,24 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/smonish777/</t>
+          <t>https://leetcode.com/u/tharik25/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>922525106249</t>
+          <t>922525106199</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>RENOFIYA HASIN A</t>
+          <t>MONISH S</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Renofiya-2007</t>
+          <t>smonish777</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6805,24 +6805,24 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Renofiya-2007/</t>
+          <t>https://leetcode.com/u/smonish777/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>922525106250</t>
+          <t>922525106249</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>RESMHI S</t>
+          <t>RENOFIYA HASIN A</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>reshmi2008</t>
+          <t>Renofiya-2007</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6832,24 +6832,24 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/reshmi2008/</t>
+          <t>https://leetcode.com/u/Renofiya-2007/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>922525106252</t>
+          <t>922525106250</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>RETHISH</t>
+          <t>RESMHI S</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Rethish_R</t>
+          <t>reshmi2008</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rethish_R/</t>
+          <t>https://leetcode.com/u/reshmi2008/</t>
         </is>
       </c>
     </row>
@@ -6893,27 +6893,27 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106252</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>RETHISH</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>Rethish_R</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/Rethish_R/</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>HARIJT VASAN S V</t>
+          <t>HARJIT VASAN SV</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>SANJEVI P</t>
+          <t>Sanjevi P</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>RITHIK I</t>
+          <t>Rithik I</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -1,17 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$369</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -29,23 +27,17 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,14 +45,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,15 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E369"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -458,11 +449,6 @@
           <t>Section</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LeetCode Link</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,11 +471,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/saran32/</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,11 +493,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/dharshinideivasigamani/</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,11 +515,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,11 +537,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -593,11 +559,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -620,11 +581,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/8925787430/</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -647,11 +603,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,11 +625,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -701,11 +647,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -728,11 +669,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,11 +691,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -782,11 +713,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -809,11 +735,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -836,11 +757,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/9043374912/</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +779,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,11 +801,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -917,11 +823,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/shivani208/</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -944,11 +845,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -971,11 +867,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -998,11 +889,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1025,11 +911,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1052,11 +933,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1079,11 +955,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1106,11 +977,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1133,11 +999,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1160,11 +1021,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/santhoshsathya260/</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1187,11 +1043,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1214,11 +1065,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1241,11 +1087,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1268,11 +1109,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1295,11 +1131,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1322,11 +1153,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1349,11 +1175,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1376,11 +1197,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1403,11 +1219,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1430,11 +1241,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1457,11 +1263,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1484,11 +1285,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1511,11 +1307,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1538,11 +1329,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1565,11 +1351,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1592,11 +1373,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1619,11 +1395,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1646,11 +1417,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1673,11 +1439,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1700,11 +1461,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1727,11 +1483,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1754,11 +1505,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1781,11 +1527,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1808,11 +1549,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1835,11 +1571,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sethupathi_1228/</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1862,11 +1593,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1889,11 +1615,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1916,11 +1637,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1943,11 +1659,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1970,11 +1681,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1997,11 +1703,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2024,11 +1725,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2051,11 +1747,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2078,11 +1769,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2105,11 +1791,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sujith45/</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2132,11 +1813,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2159,11 +1835,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2186,11 +1857,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2213,11 +1879,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2240,11 +1901,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2267,11 +1923,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2294,11 +1945,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2321,11 +1967,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2348,11 +1989,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2375,11 +2011,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2402,11 +2033,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2429,11 +2055,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2456,11 +2077,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2483,11 +2099,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2510,11 +2121,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2537,11 +2143,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2564,11 +2165,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2591,11 +2187,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2618,11 +2209,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2645,11 +2231,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2672,11 +2253,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2699,11 +2275,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2726,11 +2297,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2753,11 +2319,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2780,11 +2341,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2807,11 +2363,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2834,11 +2385,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2861,11 +2407,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/mahi/</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2888,11 +2429,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2915,11 +2451,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/subika1112/</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2942,11 +2473,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2969,11 +2495,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2996,11 +2517,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3023,11 +2539,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3050,11 +2561,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3077,11 +2583,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3104,11 +2605,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3131,11 +2627,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3158,11 +2649,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3185,11 +2671,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3212,11 +2693,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3239,11 +2715,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3266,11 +2737,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3293,11 +2759,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3320,11 +2781,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3347,11 +2803,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vaish200/</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3374,11 +2825,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3401,11 +2847,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3428,11 +2869,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3455,11 +2891,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3482,11 +2913,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3509,11 +2935,6 @@
           <t>ECE F</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vasuki/</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3536,11 +2957,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SAJISH7/</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3563,11 +2979,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/zklXTc9UAp/</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3590,11 +3001,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sanjayan31/</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3617,11 +3023,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sathana-1267/</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3644,11 +3045,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/shandoshsai/</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3671,11 +3067,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sharukesh2008/</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3698,11 +3089,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/krish-2007/</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3725,11 +3111,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itz_lakshe/</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3752,11 +3133,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/lavilavanya/</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3779,11 +3155,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/LING2007/</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3806,11 +3177,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/LogadharshiniT/</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3833,11 +3199,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Loga07/</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3860,11 +3221,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/loga16/</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3887,11 +3243,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3914,11 +3265,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/LOHITH012008/</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3941,11 +3287,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/LOKRAJI6793/</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3968,11 +3309,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/jenita0206/</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3995,11 +3331,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Madhankumar861053/</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4022,11 +3353,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4049,11 +3375,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Madhumitha42/</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4076,11 +3397,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Madhupkishor_20/</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4103,11 +3419,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4130,11 +3441,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/maha_lakh_20/</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4157,11 +3463,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4184,11 +3485,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4211,11 +3507,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Manoj_1319/</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4238,11 +3529,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/m____a____n____o____/</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4265,11 +3551,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/mathesh25/</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4292,11 +3573,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Mayakannan129/</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4319,11 +3595,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Mayuka_M/</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4346,11 +3617,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/milan190308/</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4373,11 +3639,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itsmoni/</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4400,11 +3661,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Monishav2007/</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4427,11 +3683,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/morrishd/</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4454,11 +3705,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4481,11 +3727,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Moushmi_20/</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4508,11 +3749,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/mythilimurugesan/</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4535,11 +3771,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4562,11 +3793,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/nandhini546/</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4589,11 +3815,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/lnavaneethan08/</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4616,11 +3837,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/NAVEETHAN/</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4643,11 +3859,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/niranjani_123/</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4670,11 +3881,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Nithishct123/</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4697,11 +3903,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Nithish_P_CS/</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4724,11 +3925,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/nithishramalingam007/</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4751,11 +3947,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/nithishwaran25/</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4778,11 +3969,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/NithyashreeG10/</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4805,11 +3991,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Nithyashree273/</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4832,11 +4013,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Nithyasri2008/</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4859,11 +4035,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/paargavi2007/</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4886,11 +4057,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/pavithra145/</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4913,11 +4079,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Pavithran_S_/</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4940,11 +4101,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Piraveen2025/</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4967,11 +4123,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_d_Prabhakaran_/</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4994,11 +4145,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/pradhosh/</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5021,11 +4167,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/pragalathan070108/</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5048,11 +4189,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Pranesh-Y/</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5075,11 +4211,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/pranithaashree/</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5102,11 +4233,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/praveen1247/</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5129,11 +4255,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/praveen_3208/</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5156,11 +4277,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5183,11 +4299,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itz_praveen_/</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5210,11 +4321,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/preethy2007/</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5237,11 +4343,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/prithiv16/</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5264,11 +4365,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/priyadharshini1551/</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5291,11 +4387,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Priyankaashok1201/</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5318,11 +4409,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/priyankadhanush23/</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5345,11 +4431,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5372,11 +4453,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/ragunath24/</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5399,11 +4475,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/rahulkajan/</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5426,11 +4497,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5453,11 +4519,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/RANJANA_2007/</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5480,11 +4541,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/RASIKA_2008/</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5507,11 +4563,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rathish2025/</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5534,11 +4585,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Ravikumar_14/</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5561,11 +4607,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/logesh2008/</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5588,11 +4629,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/ADHITHMITHRAN/</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5615,11 +4651,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/2/</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5642,11 +4673,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/arul2008/</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5669,11 +4695,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Bharanidharan_2007/</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5696,11 +4717,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/3/</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5723,11 +4739,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/4/</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5750,11 +4761,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/5/</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5777,11 +4783,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106011/</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5804,11 +4805,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106049/</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5831,11 +4827,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106052/</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5858,11 +4849,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106055/</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5885,11 +4871,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106093/</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5912,11 +4893,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106096/</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5939,11 +4915,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106097/</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5966,11 +4937,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/2007darshan/</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5993,11 +4959,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6020,11 +4981,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6047,11 +5003,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6074,11 +5025,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Anbarasu28122007/</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6101,11 +5047,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6128,11 +5069,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6155,11 +5091,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/anuja008/</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6182,11 +5113,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/B/</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6209,11 +5135,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/barani_7/</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6236,11 +5157,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Benov_18/</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6263,11 +5179,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/BhavanBala/</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6290,11 +5201,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/BK5226221/</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6317,11 +5223,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Boobase/</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6344,11 +5245,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/boomikat123/</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6371,11 +5267,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6398,11 +5289,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Brindha_S/</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6425,11 +5311,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6452,11 +5333,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/charu120108/</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6479,11 +5355,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/charunethra07/</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6506,11 +5377,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/codewithakshaya/</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6533,11 +5399,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/codewithakshaya78/</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6560,11 +5421,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Dakshinya555/</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6587,11 +5443,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6614,11 +5465,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/dejasri/</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6641,11 +5487,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/jakabesj/</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6668,11 +5509,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/jasvanthram/</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6695,11 +5531,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/UJw4zUNnJJ/</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6722,11 +5553,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/S_T_Arul/</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6749,11 +5575,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vsdharsini/</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6776,11 +5597,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/tharik25/</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6803,11 +5619,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/smonish777/</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6830,11 +5641,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Renofiya-2007/</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6857,11 +5663,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/reshmi2008/</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6884,11 +5685,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/rethanya38/</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6911,11 +5707,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rethish_R/</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6938,11 +5729,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/aashifasahanaj/</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6965,11 +5751,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/AAZHIGA/</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6992,11 +5773,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Abinaya7095/</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7019,11 +5795,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/abirami8072/</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7046,11 +5817,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/agatheeswarank/</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7073,11 +5839,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/codewithaish/</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7100,11 +5861,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Akshara015/</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7127,11 +5883,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Alageshwaran2008/</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7154,11 +5905,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7181,11 +5927,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Anusri_2008/</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7208,11 +5949,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/ANUSYA_30/</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7235,11 +5971,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Arunravi1810/</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7262,11 +5993,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Arunkumar2008/</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7289,11 +6015,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/arunprasanth6435/</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7316,11 +6037,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Arvin/</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7343,11 +6059,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/ASHOKKUMAR18/</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7370,11 +6081,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/1/</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7397,11 +6103,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/BharathwajX/</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7424,11 +6125,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/chinnappanrajniselvi/</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7451,11 +6147,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/desmashalini/</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7478,11 +6169,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Devaece/</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7505,11 +6191,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Dhaksesh_Pranav_P/</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7532,11 +6213,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Dhanasri_r/</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7559,11 +6235,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106064/</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7586,11 +6257,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106065/</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7613,11 +6279,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106066/</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7640,11 +6301,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106067/</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7667,11 +6323,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/dharaneeshk/</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7694,11 +6345,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106069/</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -7721,11 +6367,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106070/</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -7748,11 +6389,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106071/</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -7775,11 +6411,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106072/</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7802,11 +6433,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106073/</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7829,11 +6455,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Dharshini_74/</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7856,11 +6477,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106075/</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7883,11 +6499,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106077/</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7910,11 +6521,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106078/</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7937,11 +6543,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106079/</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7964,11 +6565,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kathir__21/</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7991,11 +6587,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/DhivakarR/</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8018,11 +6609,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106081/</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8045,11 +6631,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106099/</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8072,11 +6653,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106106/</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8099,11 +6675,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Dinesh_106082/</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8126,11 +6697,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106083/</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -8153,11 +6719,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106084/</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -8180,11 +6741,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106085/</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8207,11 +6763,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/princess-nk/</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8234,11 +6785,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106087/</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8261,11 +6807,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106088/</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8288,11 +6829,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106089/</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8315,11 +6851,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106090/</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8342,11 +6873,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106091/</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8369,11 +6895,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106092/</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8396,11 +6917,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8423,11 +6939,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/gomathi_0709/</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -8450,11 +6961,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106098/</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -8477,11 +6983,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106100/</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -8504,11 +7005,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922524106101/</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -8531,11 +7027,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106106/</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -8558,11 +7049,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106103/</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -8585,11 +7071,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106104/</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -8612,11 +7093,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Gowtham_080/</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -8639,11 +7115,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Gunashree20/</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -8666,11 +7137,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106108/</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -8693,11 +7159,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106109/</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -8720,11 +7181,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106110/</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -8747,11 +7203,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106111/</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -8774,11 +7225,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106112/</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -8801,11 +7247,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106113/</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -8828,11 +7269,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106114/</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -8855,11 +7291,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106115/</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -8882,11 +7313,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106116/</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -8909,11 +7335,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106117/</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -8936,11 +7357,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106118/</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -8963,11 +7379,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -8990,11 +7401,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106120/</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -9017,11 +7423,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -9044,11 +7445,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106121/</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -9071,11 +7467,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106122/</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -9098,11 +7489,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106123/</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -9125,11 +7511,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106124/</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -9152,11 +7533,6 @@
           <t>ECE B</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/922525106126/</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -9179,11 +7555,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/janani_asohkan/</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -9206,11 +7577,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/jashvanth2007/</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -9233,11 +7599,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/jayasakthi_25/</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -9260,11 +7621,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/jeevanbala142008/</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -9287,11 +7643,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/dharshanjeeva/</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -9314,11 +7665,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/jeevanaa_174_/</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -9341,11 +7687,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Jerry2008/</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -9368,11 +7709,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Joshi_666/</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -9395,11 +7731,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Jothiharshan16/</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -9422,11 +7753,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Jothi-/</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -9449,11 +7775,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_kamalini_/</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -9476,11 +7797,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/26kanishka/</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -9503,11 +7819,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kanithraakila/</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -9530,11 +7841,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Karishma_m_08/</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -9557,11 +7863,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -9584,11 +7885,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/karshana_234/</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -9611,11 +7907,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Karthi270827/</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -9638,11 +7929,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kavimalar08/</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -9665,11 +7951,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/KAVIN__26/</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -9692,11 +7973,6 @@
           <t>ECE A</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/AjaykumarAL/</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -9719,11 +7995,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kavinleet/</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -9746,11 +8017,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_kavipriya_16/</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -9773,11 +8039,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -9800,11 +8061,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kavi12d/</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -9827,11 +8083,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -9854,11 +8105,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itzz__kavya02/</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -9881,11 +8127,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/27kayalvizhi/</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -9908,11 +8149,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/keerthana_19selvam/</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -9935,11 +8171,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/KESAVINI892/</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -9962,11 +8193,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -9989,11 +8215,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kohul_v/</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -10016,11 +8237,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kowshikm23/</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -10043,11 +8259,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kowshik_rk_/</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -10070,11 +8281,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Kowshika08/</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -10097,11 +8303,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -10124,11 +8325,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -10151,11 +8347,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Harjit_Vasan/</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -10178,11 +8369,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/LOHITH1206/</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -10205,11 +8391,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sanjay_Sakthivel-2/</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -10232,11 +8413,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SATHYAPRAKASAM__7/</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -10259,11 +8435,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kanishkumar2008/</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -10286,11 +8457,6 @@
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Kishore9225/</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -10313,11 +8479,6 @@
           <t>ECE D</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Nethra777/</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -10340,11 +8501,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sanjevi007/</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -10367,11 +8523,6 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/arunkumar1004/</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -10394,14 +8545,8 @@
           <t>ECE E</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Rithik2008/</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E369"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -1,15 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$369</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -27,17 +29,23 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,20 +53,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,8 +427,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D369"/>
+  <dimension ref="A1:E369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -449,6 +458,11 @@
           <t>Section</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LeetCode Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +485,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saran32/</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,6 +512,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dharshinideivasigamani/</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -515,6 +539,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh7811/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -537,6 +566,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -559,6 +593,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -581,6 +620,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/8925787430/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -603,6 +647,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -625,6 +674,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -647,6 +701,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -669,6 +728,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -691,6 +755,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -713,6 +782,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -735,6 +809,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -757,6 +836,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/9043374912/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -779,6 +863,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -801,6 +890,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -823,6 +917,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shivani208/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -845,6 +944,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sharath_1010/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -867,6 +971,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -889,6 +998,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -911,6 +1025,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -933,6 +1052,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -955,6 +1079,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -977,6 +1106,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -999,6 +1133,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvax07/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1021,6 +1160,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhoshsathya260/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1043,6 +1187,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1065,6 +1214,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithik_78/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1087,6 +1241,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithish_/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1109,6 +1268,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1131,6 +1295,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1153,6 +1322,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saswin_88/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1175,6 +1349,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1197,6 +1376,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1219,6 +1403,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1241,6 +1430,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shreecharan22/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1263,6 +1457,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sarika_5408/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1285,6 +1484,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/roshan2403/</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1307,6 +1511,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1329,6 +1538,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1351,6 +1565,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1373,6 +1592,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1395,6 +1619,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1417,6 +1646,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1439,6 +1673,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1461,6 +1700,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjay00675/</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1483,6 +1727,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanmathi06/</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1505,6 +1754,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhiya0202/</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1527,6 +1781,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh2407/</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1549,6 +1808,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh8760/</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1571,6 +1835,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sethupathi_1228/</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1593,6 +1862,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1615,6 +1889,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1637,6 +1916,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1659,6 +1943,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1681,6 +1970,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1703,6 +1997,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1725,6 +2024,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1747,6 +2051,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1769,6 +2078,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1791,6 +2105,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sujith45/</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1813,6 +2132,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/thirishavsb/</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1835,6 +2159,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1857,6 +2186,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1879,6 +2213,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1901,6 +2240,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1923,6 +2267,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vishwajeth/</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1945,6 +2294,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/THIRINESHKUMAR0608/</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1967,6 +2321,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1989,6 +2348,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/yazhini2007/</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2011,6 +2375,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2033,6 +2402,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2055,6 +2429,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AK_Siva/</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2077,6 +2456,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivatharun22/</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2099,6 +2483,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_sobika_R/</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2121,6 +2510,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2143,6 +2537,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2165,6 +2564,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2187,6 +2591,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/syokeswaran/</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2209,6 +2618,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sri1540/</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2231,6 +2645,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sriheera03/</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2253,6 +2672,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kanth2008/</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2275,6 +2699,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2297,6 +2726,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2319,6 +2753,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2341,6 +2780,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2363,6 +2807,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2385,6 +2834,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2407,6 +2861,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahi/</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2429,6 +2888,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Subarna_17/</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2451,6 +2915,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/subika1112/</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2473,6 +2942,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sudharsan/</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2495,6 +2969,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2517,6 +2996,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sugi_07/</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2539,6 +3023,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2561,6 +3050,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sumithra_16/</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2583,6 +3077,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2605,6 +3104,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Susidharan147/</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2627,6 +3131,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sutharshana743/</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2649,6 +3158,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2671,6 +3185,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2693,6 +3212,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/thamarai_04/</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2715,6 +3239,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Thameem_786/</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2737,6 +3266,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2759,6 +3293,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2781,6 +3320,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/thiru0211_/</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2803,6 +3347,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vaish200/</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2825,6 +3374,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2847,6 +3401,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2869,6 +3428,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2891,6 +3455,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2913,6 +3482,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2935,6 +3509,11 @@
           <t>ECE F</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vasuki/</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2957,6 +3536,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SAJISH7/</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2979,6 +3563,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/zklXTc9UAp/</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3001,6 +3590,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjayan31/</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3023,6 +3617,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sathana-1267/</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3045,6 +3644,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shandoshsai/</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3067,6 +3671,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sharukesh2008/</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3089,6 +3698,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/krish-2007/</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3111,6 +3725,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz_lakshe/</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3133,6 +3752,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/lavilavanya/</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3155,6 +3779,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LING2007/</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3177,6 +3806,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LogadharshiniT/</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3199,6 +3833,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Loga07/</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3221,6 +3860,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/loga16/</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3243,6 +3887,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3265,6 +3914,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOHITH012008/</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3287,6 +3941,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOKRAJI6793/</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3309,6 +3968,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jenita0206/</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3331,6 +3995,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Madhankumar861053/</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3353,6 +4022,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/madhudhara/</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3375,6 +4049,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Madhumitha42/</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3397,6 +4076,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Madhupkishor_20/</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3419,6 +4103,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3441,6 +4130,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/maha_lakh_20/</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3463,6 +4157,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3485,6 +4184,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/manishaa_20/</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3507,6 +4211,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Manoj_1319/</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3529,6 +4238,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3551,6 +4265,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mathesh25/</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3573,6 +4292,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mayakannan129/</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3595,6 +4319,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mayuka_M/</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3617,6 +4346,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/milan190308/</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3639,6 +4373,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itsmoni/</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3661,6 +4400,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Monishav2007/</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3683,6 +4427,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/morrishd/</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3705,6 +4454,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3727,6 +4481,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Moushmi_20/</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3749,6 +4508,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mythilimurugesan/</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3771,6 +4535,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3793,6 +4562,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nandhini546/</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3815,6 +4589,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/lnavaneethan08/</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3837,6 +4616,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/NAVEETHAN/</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3859,6 +4643,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/niranjani_123/</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3881,6 +4670,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithishct123/</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3903,6 +4697,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithish_P_CS/</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3925,6 +4724,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nithishramalingam007/</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3947,6 +4751,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nithishwaran25/</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3969,6 +4778,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/NithyashreeG10/</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3991,6 +4805,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithyashree273/</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4013,6 +4832,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithyasri2008/</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4035,6 +4859,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/paargavi2007/</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4057,6 +4886,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pavithra145/</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4079,6 +4913,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pavithran_S_/</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4101,6 +4940,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Piraveen2025/</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4123,6 +4967,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_d_Prabhakaran_/</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4145,6 +4994,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pradhosh/</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4167,6 +5021,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pragalathan070108/</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4189,6 +5048,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pranesh-Y/</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4211,6 +5075,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pranithaashree/</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4233,6 +5102,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/praveen1247/</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4255,6 +5129,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/praveen_3208/</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4277,6 +5156,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4299,6 +5183,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz_praveen_/</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4321,6 +5210,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/preethy2007/</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4343,6 +5237,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/prithiv16/</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4365,6 +5264,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/priyadharshini1551/</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4387,6 +5291,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Priyankaashok1201/</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4409,6 +5318,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/priyankadhanush23/</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4431,6 +5345,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4453,6 +5372,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ragunath24/</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4475,6 +5399,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/rahulkajan/</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4497,6 +5426,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4519,6 +5453,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RANJANA_2007/</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4541,6 +5480,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RASIKA_2008/</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4563,6 +5507,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rathish2025/</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4585,6 +5534,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Ravikumar_14/</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4607,6 +5561,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/logesh2008/</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4629,6 +5588,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ADHITHMITHRAN/</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4651,6 +5615,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/2/</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4673,6 +5642,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arul2008/</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4695,6 +5669,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Bharanidharan_2007/</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4717,6 +5696,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/3/</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4739,6 +5723,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/4/</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4761,6 +5750,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/5/</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4783,6 +5777,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106011/</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4805,6 +5804,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106049/</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4827,6 +5831,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106052/</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4849,6 +5858,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106055/</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4871,6 +5885,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106093/</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4893,6 +5912,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106096/</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4915,6 +5939,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106097/</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4937,6 +5966,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/2007darshan/</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4959,6 +5993,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/afton_2008/</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4981,6 +6020,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5003,6 +6047,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5025,6 +6074,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5047,6 +6101,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5069,6 +6128,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5091,6 +6155,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/anuja008/</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5113,6 +6182,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/B/</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5135,6 +6209,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/barani_7/</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5157,6 +6236,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Benov_18/</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5179,6 +6263,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BhavanBala/</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5201,6 +6290,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BK5226221/</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5223,6 +6317,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Boobase/</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5245,6 +6344,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/boomikat123/</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5267,6 +6371,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5289,6 +6398,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Brindha_S/</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5311,6 +6425,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5333,6 +6452,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/charu120108/</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5355,6 +6479,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/charunethra07/</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5377,6 +6506,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/codewithakshaya/</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5399,6 +6533,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/codewithakshaya78/</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5421,6 +6560,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5443,6 +6587,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5465,6 +6614,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dejasri/</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5487,6 +6641,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jakabesj/</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5509,6 +6668,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jasvanthram/</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5531,6 +6695,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/UJw4zUNnJJ/</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5553,6 +6722,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/S_T_Arul/</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5575,6 +6749,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vsdharsini/</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5597,6 +6776,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/tharik25/</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5619,6 +6803,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/smonish777/</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5641,6 +6830,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Renofiya-2007/</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5663,6 +6857,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/reshmi2008/</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5685,6 +6884,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/rethanya38/</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5707,6 +6911,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rethish_R/</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5729,6 +6938,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/aashifasahanaj/</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5751,6 +6965,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AAZHIGA/</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5773,6 +6992,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Abinaya7095/</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5795,6 +7019,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/abirami8072/</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5817,6 +7046,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/agatheeswarank/</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5839,6 +7073,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/codewithaish/</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5861,6 +7100,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Akshara015/</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5883,6 +7127,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Alageshwaran2008/</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5905,6 +7154,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5927,6 +7181,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anusri_2008/</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5949,6 +7208,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ANUSYA_30/</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5971,6 +7235,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Arunravi1810/</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5993,6 +7262,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Arunkumar2008/</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6015,6 +7289,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arunprasanth6435/</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6037,6 +7316,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Arvin/</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6059,6 +7343,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ASHOKKUMAR18/</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6081,6 +7370,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/1/</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6103,6 +7397,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BharathwajX/</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6125,6 +7424,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/chinnappanrajniselvi/</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6147,6 +7451,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/desmashalini/</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6169,6 +7478,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Devaece/</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6191,6 +7505,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dhaksesh_Pranav_P/</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6213,6 +7532,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dhanasri_r/</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6235,6 +7559,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106064/</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6257,6 +7586,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106065/</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6279,6 +7613,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106066/</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6301,6 +7640,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106067/</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6323,6 +7667,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dharaneeshk/</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6345,6 +7694,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106069/</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6367,6 +7721,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106070/</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6389,6 +7748,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106071/</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6411,6 +7775,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106072/</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6433,6 +7802,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106073/</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6455,6 +7829,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dharshini_74/</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6477,6 +7856,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106075/</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6499,6 +7883,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106077/</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6521,6 +7910,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106078/</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6543,6 +7937,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106079/</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6565,6 +7964,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kathir__21/</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6587,6 +7991,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/DhivakarR/</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6609,6 +8018,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106081/</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6631,6 +8045,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106099/</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6653,6 +8072,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106106/</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6675,6 +8099,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dinesh_106082/</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6697,6 +8126,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106083/</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6719,6 +8153,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106084/</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6741,6 +8180,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106085/</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6763,6 +8207,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/princess-nk/</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6785,6 +8234,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106087/</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6807,6 +8261,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106088/</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6829,6 +8288,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106089/</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6851,6 +8315,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106090/</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6873,6 +8342,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106091/</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6895,6 +8369,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106092/</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6917,6 +8396,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6939,6 +8423,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/gomathi_0709/</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6961,6 +8450,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106098/</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6983,6 +8477,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106100/</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7005,6 +8504,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922524106101/</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7027,6 +8531,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106106/</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7049,6 +8558,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106103/</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7071,6 +8585,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106104/</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7093,6 +8612,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Gowtham_080/</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7115,6 +8639,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Gunashree20/</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7137,6 +8666,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106108/</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7159,6 +8693,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106109/</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7181,6 +8720,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106110/</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7203,6 +8747,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106111/</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7225,6 +8774,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106112/</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7247,6 +8801,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106113/</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7269,6 +8828,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106114/</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7291,6 +8855,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106115/</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7313,6 +8882,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106116/</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7335,6 +8909,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106117/</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7357,6 +8936,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106118/</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7379,6 +8963,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7401,6 +8990,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106120/</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7423,6 +9017,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7445,6 +9044,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106121/</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7467,6 +9071,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106122/</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7489,6 +9098,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106123/</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7511,6 +9125,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106124/</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7533,6 +9152,11 @@
           <t>ECE B</t>
         </is>
       </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106126/</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7555,6 +9179,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7577,6 +9206,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jashvanth2007/</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7599,6 +9233,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jayasakthi_25/</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7621,6 +9260,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jeevanbala142008/</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7643,6 +9287,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dharshanjeeva/</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7665,6 +9314,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jeevanaa_174_/</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7687,6 +9341,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jerry2008/</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7709,6 +9368,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Joshi_666/</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7731,6 +9395,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jothiharshan16/</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7753,6 +9422,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jothi-/</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7775,6 +9449,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_kamalini_/</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7797,6 +9476,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/26kanishka/</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7819,6 +9503,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kanithraakila/</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7841,6 +9530,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Karishma_m_08/</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7863,6 +9557,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/karmukilan567/</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7885,6 +9584,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/karshana_234/</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7907,6 +9611,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Karthi270827/</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7929,6 +9638,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavimalar08/</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7951,6 +9665,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KAVIN__26/</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7973,6 +9692,11 @@
           <t>ECE A</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AjaykumarAL/</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7995,6 +9719,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavinleet/</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8017,6 +9746,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_kavipriya_16/</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8039,6 +9773,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8061,6 +9800,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavi12d/</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8083,6 +9827,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahi20_/</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8105,6 +9854,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itzz__kavya02/</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8127,6 +9881,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8149,6 +9908,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/keerthana_19selvam/</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8171,6 +9935,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KESAVINI892/</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8193,6 +9962,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8215,6 +9989,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kohul_v/</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8237,6 +10016,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshikm23/</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8259,6 +10043,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshik_rk_/</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8281,6 +10070,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Kowshika08/</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8303,6 +10097,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8325,6 +10124,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8347,6 +10151,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Harjit_Vasan/</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8369,6 +10178,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOHITH1206/</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8391,6 +10205,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sanjay_Sakthivel-2/</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8413,6 +10232,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SATHYAPRAKASAM__7/</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8435,6 +10259,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kanishkumar2008/</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8457,6 +10286,11 @@
           <t>ECE C</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Kishore9225/</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8479,6 +10313,11 @@
           <t>ECE D</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nethra777/</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8501,6 +10340,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjevi007/</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8523,6 +10367,11 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arunkumar1004/</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8545,8 +10394,14 @@
           <t>ECE E</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithik2008/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E369"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -521,17 +521,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
@@ -764,17 +764,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>santhosh s</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>santhoshsathya260</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhoshsathya260/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>santhosh s</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhoshsathya260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhoshsathya260/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,14 +919,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sarveswaran R</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SASHMIKA P</t>
+          <t>Sarveswaran R</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106293</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>saswin D</t>
+          <t>SASHMIKA P</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
@@ -1601,17 +1601,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106293</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sahana.v</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
@@ -1682,17 +1682,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SABAREESH</t>
+          <t>sahana.v</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SABAREESH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sanjay U</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>Sanjay U</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
